--- a/Excel Assignment 28 Feb 25.xlsx
+++ b/Excel Assignment 28 Feb 25.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03143e4fab820a82/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03143e4fab820a82/Documents/GitHub/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06980A92-B80E-47D1-A77F-910321B0BED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{06980A92-B80E-47D1-A77F-910321B0BED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A299FE94-A33B-4B5F-A903-8EC6F4B34740}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{3305FB62-B19C-4342-AEBB-31F92B1092EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,12 +28,18 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t xml:space="preserve">Just a check </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -384,6 +391,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC1A39D-7CE5-401A-B127-B0FA07E21E8B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C0F100-A20E-4E23-B9E0-AB2B2B06BC50}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
